--- a/postman/SAT-Datashare-SAPI-PAPI-EAPI-payloads (2) (1).xlsx
+++ b/postman/SAT-Datashare-SAPI-PAPI-EAPI-payloads (2) (1).xlsx
@@ -4662,12 +4662,24 @@
           <t>presandbox</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>(set on the Presandbox folder)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>(set on the Presandbox folder)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>(set on the Presandbox folder)</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Paste hosts when the presandbox apps are deployed. Collection uses {{exp_base}} / {{papi_base}} / {{sapi_base}}.</t>
+          <t>One Postman collection. Open the Presandbox folder and paste the three hosts on that folder.</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4689,24 @@
           <t>production</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>(set on the Production folder)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>(set on the Production folder)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>(set on the Production folder)</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Paste hosts when the production apps are deployed.</t>
+          <t>One Postman collection. Open the Production folder and paste the three hosts on that folder.</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4845,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Import matching Postman environment</t>
+          <t>Folders inside the single Postman collection</t>
         </is>
       </c>
     </row>
